--- a/artfynd/A 15794-2026 artfynd.xlsx
+++ b/artfynd/A 15794-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131983229</v>
       </c>
       <c r="B2" t="n">
-        <v>58381</v>
+        <v>58383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132060776</v>
       </c>
       <c r="B4" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>132060821</v>
       </c>
       <c r="B5" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>132060808</v>
       </c>
       <c r="B6" t="n">
-        <v>58669</v>
+        <v>58671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15794-2026 artfynd.xlsx
+++ b/artfynd/A 15794-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131983229</v>
       </c>
       <c r="B2" t="n">
-        <v>58383</v>
+        <v>58384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131983212</v>
       </c>
       <c r="B3" t="n">
-        <v>57242</v>
+        <v>57243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132060776</v>
       </c>
       <c r="B4" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr</t>
+          <t>Per Muhr, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
         <v>132060821</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>132060808</v>
       </c>
       <c r="B6" t="n">
-        <v>58671</v>
+        <v>58672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>132060848</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15794-2026 artfynd.xlsx
+++ b/artfynd/A 15794-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131983229</v>
       </c>
       <c r="B2" t="n">
-        <v>58384</v>
+        <v>58388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131983212</v>
       </c>
       <c r="B3" t="n">
-        <v>57243</v>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132060776</v>
       </c>
       <c r="B4" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
         <v>132060821</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>132060808</v>
       </c>
       <c r="B6" t="n">
-        <v>58672</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>132060848</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15794-2026 artfynd.xlsx
+++ b/artfynd/A 15794-2026 artfynd.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr</t>
+          <t>Per Muhr, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr</t>
+          <t>Per Muhr, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr</t>
+          <t>Per Muhr, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 15794-2026 artfynd.xlsx
+++ b/artfynd/A 15794-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>132060776</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>132060821</v>
       </c>
       <c r="B5" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
         <v>132060808</v>
       </c>
       <c r="B6" t="n">
-        <v>58676</v>
+        <v>58677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
         <v>132060848</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 15794-2026 artfynd.xlsx
+++ b/artfynd/A 15794-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131983212</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131983229</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060808</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,8 +1479,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060650</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>